--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008566648607316726</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>51570192</v>
+        <v>4039320</v>
       </c>
       <c r="L2" t="n">
-        <v>26838777</v>
+        <v>1538215</v>
       </c>
       <c r="M2" t="n">
-        <v>6189121</v>
+        <v>276538</v>
       </c>
       <c r="N2" t="n">
-        <v>256766</v>
+        <v>4728</v>
       </c>
       <c r="O2" t="n">
-        <v>3620906</v>
+        <v>156598</v>
       </c>
       <c r="P2" t="n">
-        <v>1242042</v>
+        <v>144</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999765157699585</v>
+        <v>0.9999915957450867</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8225743770599365</v>
+        <v>0.6955493092536926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6880708932876587</v>
+        <v>0.5237749814987183</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6075053215026855</v>
+        <v>0.3757703006267548</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2082594633102417</v>
+        <v>0.03753334283828735</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6518377661705017</v>
+        <v>0.3819938600063324</v>
       </c>
       <c r="W2" t="n">
-        <v>0.81573486328125</v>
+        <v>0.2562277615070343</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002053537536211935</v>
       </c>
       <c r="C3" t="n">
-        <v>1108</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>51570192</v>
+        <v>4039320</v>
       </c>
       <c r="E3" t="n">
-        <v>8055717</v>
+        <v>837411</v>
       </c>
       <c r="F3" t="n">
-        <v>277991</v>
+        <v>43442</v>
       </c>
       <c r="G3" t="n">
-        <v>23204</v>
+        <v>3877</v>
       </c>
       <c r="H3" t="n">
-        <v>19291</v>
+        <v>4419</v>
       </c>
       <c r="I3" t="n">
-        <v>703</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>120197685</v>
+        <v>10016569</v>
       </c>
       <c r="K3" t="n">
-        <v>124883533</v>
+        <v>9633029</v>
       </c>
       <c r="L3" t="n">
-        <v>144300844</v>
+        <v>11585561</v>
       </c>
       <c r="M3" t="n">
-        <v>180714717</v>
+        <v>14924684</v>
       </c>
       <c r="N3" t="n">
-        <v>193905459</v>
+        <v>16118291</v>
       </c>
       <c r="O3" t="n">
-        <v>187895260</v>
+        <v>15563255</v>
       </c>
       <c r="P3" t="n">
-        <v>193352042</v>
+        <v>16135132</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8602457642555237</v>
+        <v>0.8195824027061462</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6796811819076538</v>
+        <v>0.4597906768321991</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5505434274673462</v>
+        <v>0.2924684584140778</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2391651272773743</v>
+        <v>0.05249308794736862</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5910788774490356</v>
+        <v>0.3052628338336945</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5347647666931152</v>
+        <v>0.0007420767797157168</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03228002292548469</v>
       </c>
       <c r="C4" t="n">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10188400</v>
+        <v>1556794</v>
       </c>
       <c r="E4" t="n">
-        <v>26838777</v>
+        <v>1538215</v>
       </c>
       <c r="F4" t="n">
-        <v>2071552</v>
+        <v>196819</v>
       </c>
       <c r="G4" t="n">
-        <v>137058</v>
+        <v>19105</v>
       </c>
       <c r="H4" t="n">
-        <v>236331</v>
+        <v>34460</v>
       </c>
       <c r="I4" t="n">
-        <v>15044</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>1779</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>11123461</v>
+        <v>1768061</v>
       </c>
       <c r="L4" t="n">
-        <v>12167053</v>
+        <v>1398571</v>
       </c>
       <c r="M4" t="n">
-        <v>3998643</v>
+        <v>459385</v>
       </c>
       <c r="N4" t="n">
-        <v>976148</v>
+        <v>121240</v>
       </c>
       <c r="O4" t="n">
-        <v>1934013</v>
+        <v>253351</v>
       </c>
       <c r="P4" t="n">
-        <v>280563</v>
+        <v>418</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999882578849792</v>
+        <v>0.9999957680702209</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8409884572029114</v>
+        <v>0.7524889707565308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6838502883911133</v>
+        <v>0.4897016286849976</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5776234269142151</v>
+        <v>0.328927218914032</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2226448953151703</v>
+        <v>0.04377027973532677</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6199732422828674</v>
+        <v>0.3393449187278748</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6460220813751221</v>
+        <v>0.001479867612943053</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>672682</v>
+        <v>154763</v>
       </c>
       <c r="E5" t="n">
-        <v>3271470</v>
+        <v>406347</v>
       </c>
       <c r="F5" t="n">
-        <v>6189121</v>
+        <v>276538</v>
       </c>
       <c r="G5" t="n">
-        <v>297649</v>
+        <v>31389</v>
       </c>
       <c r="H5" t="n">
-        <v>752265</v>
+        <v>76400</v>
       </c>
       <c r="I5" t="n">
-        <v>58552</v>
+        <v>89</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8378014</v>
+        <v>889190</v>
       </c>
       <c r="L5" t="n">
-        <v>12648526</v>
+        <v>1807253</v>
       </c>
       <c r="M5" t="n">
-        <v>5052719</v>
+        <v>668993</v>
       </c>
       <c r="N5" t="n">
-        <v>816827</v>
+        <v>85341</v>
       </c>
       <c r="O5" t="n">
-        <v>2505021</v>
+        <v>356396</v>
       </c>
       <c r="P5" t="n">
-        <v>1080553</v>
+        <v>193906</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999909400939941</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9004799127578735</v>
+        <v>0.8372739553451538</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8733609318733215</v>
+        <v>0.8036801815032959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9538090229034424</v>
+        <v>0.9308998584747314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908500909805298</v>
+        <v>0.987349271774292</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9773467183113098</v>
+        <v>0.962660014629364</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9930539727210999</v>
+        <v>0.9880998730659485</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>181834</v>
+        <v>26538</v>
       </c>
       <c r="E6" t="n">
-        <v>246117</v>
+        <v>26985</v>
       </c>
       <c r="F6" t="n">
-        <v>275111</v>
+        <v>23962</v>
       </c>
       <c r="G6" t="n">
-        <v>256766</v>
+        <v>4728</v>
       </c>
       <c r="H6" t="n">
-        <v>105044</v>
+        <v>7795</v>
       </c>
       <c r="I6" t="n">
-        <v>8609</v>
+        <v>54</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>74588</v>
+        <v>26811</v>
       </c>
       <c r="E7" t="n">
-        <v>539031</v>
+        <v>113651</v>
       </c>
       <c r="F7" t="n">
-        <v>1246033</v>
+        <v>163799</v>
       </c>
       <c r="G7" t="n">
-        <v>447600</v>
+        <v>51948</v>
       </c>
       <c r="H7" t="n">
-        <v>3620906</v>
+        <v>156598</v>
       </c>
       <c r="I7" t="n">
-        <v>197655</v>
+        <v>179</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>5957</v>
+        <v>3155</v>
       </c>
       <c r="E8" t="n">
-        <v>54718</v>
+        <v>14177</v>
       </c>
       <c r="F8" t="n">
-        <v>127956</v>
+        <v>31363</v>
       </c>
       <c r="G8" t="n">
-        <v>70637</v>
+        <v>14921</v>
       </c>
       <c r="H8" t="n">
-        <v>821082</v>
+        <v>130277</v>
       </c>
       <c r="I8" t="n">
-        <v>1242042</v>
+        <v>144</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
